--- a/03-data-analysis/05-charts-visualization/3.5-charts-visualization.xlsx
+++ b/03-data-analysis/05-charts-visualization/3.5-charts-visualization.xlsx
@@ -4090,7 +4090,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="171" customHeight="1">
+    <row r="8" ht="186" customHeight="1">
       <c r="A8" s="18" t="inlineStr">
         <is>
           <t>4</t>
@@ -4108,7 +4108,7 @@
         <is>
           <t>1. Each bar is drawn up from the axis minimum, so its height is its rate minus 5%.
 2. (0.1836 − 0.05) ÷ (0.0639 − 0.05) = 9.6.
-3. Fix the chart: double-click the vertical axis, and in Format Axis → Axis Options → Bounds set Minimum to 0 (or click Reset so Excel chooses 0). Turn off Vary colors by point (Format Data Series → Fill), delete the legend, add data labels, and give the chart a title that states the finding.</t>
+3. Fix the chart: double-click the vertical axis, and in Format Axis → Axis Options → Bounds set Minimum to 0 (or click Reset so Excel chooses 0). Turn off Vary colors by point (Format Data Series → Fill &amp; Line → Fill), delete the legend, add data labels, and give the chart a title that states the finding.</t>
         </is>
       </c>
       <c r="E8" cm="1" s="55">
@@ -4170,7 +4170,7 @@
       <c r="D10" s="50" t="inlineStr">
         <is>
           <t>1. On Stays, select D1:D301 (the LOSDays column with its header).
-2. Choose Insert → Insert Statistic Chart → Histogram (Mac: Insert → Statistical chart → Histogram).
+2. Choose Insert → Insert Statistic Chart → Histogram. On a Mac, the same Statistic Chart button is on the Insert tab.
 3. Double-click the horizontal axis. Under Axis Options → Bins, choose Bin width 1, tick Overflow bin and type 10, and tick Underflow bin and type 1.
 4. Hover over the last column, labeled &gt;10.</t>
         </is>
@@ -4388,7 +4388,7 @@
       </c>
       <c r="B17" s="19" t="inlineStr">
         <is>
-          <t>Write a formula in the yellow cell that builds this chart title from tblEDMonthly: ED visits by facility, &lt;first month&gt; to &lt;last month&gt; (&lt;total visits&gt; visits). Show each month as a three-letter month and year, and the total with a thousands separator. Example of the pattern: ED visits by facility, Mar 2023 to Feb 2024 (9,876 visits). Then link your line chart's title to this cell.</t>
+          <t>Write a formula in the yellow cell that builds this chart title from tblEDMonthly: ED visits by facility, [first month] to [last month] ([total visits] visits). Show each month as a three-letter month and year, and the total with a thousands separator. Example of the pattern: ED visits by facility, Mar 2023 to Feb 2024 (9,876 visits). Then link your line chart's title to this cell.</t>
         </is>
       </c>
       <c r="C17" s="49" t="inlineStr">
@@ -5550,7 +5550,7 @@
     <row r="229">
       <c r="A229" s="3" t="inlineStr">
         <is>
-          <t>openpyxl can't draw sparklines, so compare your sparklines with the values above.</t>
+          <t>This sheet can't show sparklines, so compare your sparklines with the values above.</t>
         </is>
       </c>
     </row>
@@ -6307,7 +6307,7 @@
       </c>
       <c r="B18" s="19" t="inlineStr">
         <is>
-          <t>Write a formula in the yellow cell that builds this chart title from tblEDMonthly: ED visits by facility, &lt;first month&gt; to &lt;last month&gt; (&lt;total visits&gt; visits). Show each month as a three-letter month and year, and the total with a thousands separator. Example of the pattern: ED visits by facility, Mar 2023 to Feb 2024 (9,876 visits). Then link your line chart's title to this cell.</t>
+          <t>Write a formula in the yellow cell that builds this chart title from tblEDMonthly: ED visits by facility, [first month] to [last month] ([total visits] visits). Show each month as a three-letter month and year, and the total with a thousands separator. Example of the pattern: ED visits by facility, Mar 2023 to Feb 2024 (9,876 visits). Then link your line chart's title to this cell.</t>
         </is>
       </c>
       <c r="C18" s="20" t="inlineStr">

--- a/03-data-analysis/05-charts-visualization/3.5-charts-visualization.xlsx
+++ b/03-data-analysis/05-charts-visualization/3.5-charts-visualization.xlsx
@@ -2090,7 +2090,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Most stays last 2–5 days; 9 run past 10 days</a:t>
+              <a:t>Most stays last 2–5 days, and 9 run past 10 days</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -2909,34 +2909,34 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1F497D"/>
+        <a:srgbClr val="44546A"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="EEECE1"/>
+        <a:srgbClr val="E7E6E6"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4F81BD"/>
+        <a:srgbClr val="4472C4"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="C0504D"/>
+        <a:srgbClr val="ED7D31"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9BBB59"/>
+        <a:srgbClr val="A5A5A5"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064A2"/>
+        <a:srgbClr val="FFC000"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4BACC6"/>
+        <a:srgbClr val="5B9BD5"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="F79646"/>
+        <a:srgbClr val="70AD47"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000FF"/>
+        <a:srgbClr val="0563C1"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="800080"/>
+        <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
@@ -3389,7 +3389,7 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="33" customHeight="1">
+    <row r="22" ht="48" customHeight="1">
       <c r="B22" s="8" t="inlineStr">
         <is>
           <t>Note</t>
@@ -3397,7 +3397,7 @@
       </c>
       <c r="C22" s="7" t="inlineStr">
         <is>
-          <t>Stays → LOSDays is the exact length of stay (discharge time minus admit time, in days, rounded to 1 decimal place), so it can differ slightly from the count of midnights used in Lesson 3.4.</t>
+          <t>On the Stays sheet, LOSDays is the exact length of stay (discharge time minus admit time, in days, rounded to 1 decimal place), so it can differ slightly from the count of midnights used in Lesson 3.4.</t>
         </is>
       </c>
     </row>
@@ -3549,7 +3549,7 @@
         </is>
       </c>
     </row>
-    <row r="38" ht="63" customHeight="1">
+    <row r="38" ht="78" customHeight="1">
       <c r="B38" s="8" t="inlineStr">
         <is>
           <t>About the data</t>
@@ -3557,7 +3557,7 @@
       </c>
       <c r="C38" s="7" t="inlineStr">
         <is>
-          <t>Bluestone Health System, pre-summarized for charting: monthly ED visits by hospital with LWBS counts (Jan 2024 – Dec 2025), 2025 ED arrivals and average door-to-provider minutes by hour of day, 2025 readmission rates by service line, 2025 payer mix, a sample of 300 of the 2,859 inpatient stays that began in 2025, 2025 claim denials by reason, and 4 West's FY2025 budget-to-actual margin bridge.</t>
+          <t>Bluestone Health System, pre-summarized for charting: monthly ED visits by hospital with counts of patients who left without being seen (LWBS), Jan 2024 – Dec 2025, 2025 ED arrivals and average door-to-provider minutes by hour of day, 2025 readmission rates by service line, 2025 payer mix, a sample of 300 of the 2,859 inpatient stays that began in 2025, 2025 claim denials by reason, and 4 West's FY2025 budget-to-actual margin bridge.</t>
         </is>
       </c>
     </row>
@@ -3746,14 +3746,14 @@
     <row r="1">
       <c r="A1" s="13" t="inlineStr">
         <is>
-          <t>Lesson 3.5 · Bonus: Two charts for the operations review</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="49" customHeight="1">
+          <t>Lesson 3.5 · Bonus: Charts for the operations review</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="64" customHeight="1">
       <c r="A2" s="14" t="inlineStr">
         <is>
-          <t>Two directors bring questions to Bluestone's monthly operations review. The ED medical director believes patients leave without being seen (LWBS) mainly in busy months, and the ED's target is an LWBS rate of 2% or less. The revenue-cycle director wants to know which denial reasons to work first, ranked by dollars at risk (DeniedCharges) rather than by claim counts. Build one chart for each question and check the numbers behind them.</t>
+          <t>Two directors bring questions to Bluestone's monthly operations review. The ED medical director believes patients leave without being seen (LWBS) mainly in busy months, and the ED's target is an LWBS rate of 2% or less. The revenue-cycle director wants to know which denial reasons to work first, ranked by dollars at risk (DeniedCharges) rather than by claim counts. Build a combo chart and a scatter chart for the first question and a Pareto chart for the second, then check the numbers behind them.</t>
         </is>
       </c>
     </row>
@@ -3805,12 +3805,12 @@
       </c>
       <c r="B6" s="19" t="inlineStr">
         <is>
-          <t>On ED_Monthly, fill the yellow LWBSRate column with LWBS ÷ Total for each month and format it as a percentage. The gray cell counts the months above the 2% target. How many of the 24 months missed the target?</t>
+          <t>On ED_Monthly, fill the yellow LWBSRate column with LWBS ÷ Total for each month. The column is already formatted as a percentage. The gray cell counts the months above the 2% target. How many of the 24 months missed the target?</t>
         </is>
       </c>
       <c r="C6" s="20" t="inlineStr">
         <is>
-          <t>Type =[@LWBS]/[@Total] in the first LWBSRate cell, and the Table fills the rest</t>
+          <t>Write one formula in G2 with [@Column] references (Lesson 3.1). The Table fills the other 23 rows</t>
         </is>
       </c>
       <c r="D6" cm="1" s="44">
@@ -3879,7 +3879,7 @@
       </c>
       <c r="C9" s="20" t="inlineStr">
         <is>
-          <t>Running share: =SUM($C$2:C2)/SUM($C$2:$C$8) filled down</t>
+          <t>Follow 'A Pareto by hand' in Guide section 12. DeniedCharges is column C. Sort before you chart</t>
         </is>
       </c>
       <c r="D9" s="21" t="n"/>
@@ -4090,7 +4090,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="186" customHeight="1">
+    <row r="8" ht="261" customHeight="1">
       <c r="A8" s="18" t="inlineStr">
         <is>
           <t>4</t>
@@ -4098,7 +4098,7 @@
       </c>
       <c r="B8" s="19" t="inlineStr">
         <is>
-          <t>The Makeover sheet has a colleague's column chart of the same readmission rates. Its vertical axis starts at 5%, not 0%. Measured from that axis, how many times taller is the Cardiovascular bar than the Women &amp; Children bar? Round to 1 decimal place. Then fix the chart.</t>
+          <t>The Makeover sheet has a colleague's column chart of the same readmission rates. Its vertical axis starts at 5%, not 0%. Measured from that axis, how many times taller is the Cardiovascular bar than the Women &amp; Children bar? Round to 1 decimal place. Then fix the chart in place, using the checklist in Guide section 16, and add alt text.</t>
         </is>
       </c>
       <c r="C8" s="54" t="n">
@@ -4108,7 +4108,8 @@
         <is>
           <t>1. Each bar is drawn up from the axis minimum, so its height is its rate minus 5%.
 2. (0.1836 − 0.05) ÷ (0.0639 − 0.05) = 9.6.
-3. Fix the chart: double-click the vertical axis, and in Format Axis → Axis Options → Bounds set Minimum to 0 (or click Reset so Excel chooses 0). Turn off Vary colors by point (Format Data Series → Fill &amp; Line → Fill), delete the legend, add data labels, and give the chart a title that states the finding.</t>
+3. Fix the chart: double-click the vertical axis, and in Format Axis → Axis Options → Bounds set Minimum to 0 (or click Reset so Excel chooses 0). Turn off Vary colors by point (Format Data Series → Fill &amp; Line → Fill), delete the legend, add data labels, and give the chart a title that states the finding.
+4. Right-click the chart → Edit Alt Text and describe it, for example: Column chart of 2025 30-day readmission rates by service line. Cardiovascular is highest at 18.4% and Women &amp; Children lowest at 6.4%.</t>
         </is>
       </c>
       <c r="E8" cm="1" s="55">
@@ -4181,7 +4182,7 @@
       </c>
       <c r="F10" s="19" t="inlineStr">
         <is>
-          <t>A histogram answers "how are the values distributed?" by counting values in equal-width bins. Here the tallest bin is (3, 4] days with 75 stays, and the long right tail ends in the &gt;10 overflow bin with 9 stays. That skew is why the median LOS (3.9 days) sits below the mean (4.59). A bin label such as (3, 4] means "more than 3, up to and including 4". The overflow and underflow bins stop a few extreme stays from stretching the axis. Cross-check with a formula: =COUNTIF(tblStays[LOSDays],"&gt;10")</t>
+          <t>A histogram answers "how are the values distributed?" by counting values in equal-width bins. Here the tallest bin is (3, 4] days with 75 stays, and the long right tail ends in the &gt;10 overflow bin with 9 stays. That skew is why the median length of stay (3.90 days) sits below the mean (4.59 days). The few long stays pull the mean up but barely move the median. A bin label such as (3, 4] means "more than 3, up to and including 4". The overflow and underflow bins stop a few extreme stays from stretching the axis. Cross-check with a formula: =COUNTIF(tblStays[LOSDays],"&gt;10")</t>
         </is>
       </c>
     </row>
@@ -4250,7 +4251,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="171" customHeight="1">
+    <row r="13" ht="201" customHeight="1">
       <c r="A13" s="18" t="inlineStr">
         <is>
           <t>9</t>
@@ -4268,7 +4269,7 @@
         <is>
           <t>1. Select A1:C25 on ED_Hourly.
 2. Choose Insert → Insert Combo Chart → Clustered Column – Line on Secondary Axis. (Or insert any chart, then Chart Design → Change Chart Type → Combo, set AvgDoorToProviderMin to Line and tick its Secondary Axis box.)
-3. Add axis titles (+ → Axis Titles): Arrivals on the left and Avg minutes to provider on the right.
+3. Add axis titles with Chart Elements (+) → Axis Titles (Mac: Chart Design → Add Chart Element → Axis Titles): Arrivals on the left and Avg minutes to provider on the right.
 4. Hover over the highest point of the line.</t>
         </is>
       </c>
@@ -4278,11 +4279,11 @@
       </c>
       <c r="F13" s="19" t="inlineStr">
         <is>
-          <t>Arrivals peak at 16:00, and the average wait peaks at 13:00 (57.1 minutes, against 27.8 at 04:00). The two series use different units (visits and minutes) and very different sizes, so the line needs its own axis. Otherwise it would be squashed flat. The shapes match closely (correlation 0.96): waits grow when arrivals outpace staffing. Always title both axes on a dual-axis chart so nobody reads minutes off the arrivals scale. Cross-check with a formula: =VALUE(LEFT(XLOOKUP(MAX(tblEDHourly[AvgDoorToProviderMin]),tblEDHourly[AvgDoorToProviderMin],tblEDHourly[ArrivalHour]),2))</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="156" customHeight="1">
+          <t>Arrivals peak at 16:00, and the average wait peaks at 13:00 (57.1 minutes, against 27.8 at 04:00). The two series use different units (visits and minutes) and very different sizes, so the line needs its own axis. Otherwise it would be squashed flat. The two shapes match closely (correlation 0.96), so waits rise and fall with arrivals. That suggests staffing doesn't keep pace in the busy hours, but the chart alone can't prove the cause. Always title both axes on a dual-axis chart so nobody reads minutes off the arrivals scale. Cross-check with a formula: =VALUE(LEFT(XLOOKUP(MAX(tblEDHourly[AvgDoorToProviderMin]),tblEDHourly[AvgDoorToProviderMin],tblEDHourly[ArrivalHour]),2))</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="186" customHeight="1">
       <c r="A14" s="18" t="inlineStr">
         <is>
           <t>10</t>
@@ -4301,7 +4302,7 @@
           <t>1. Select A1:B8 on Denials.
 2. Choose Insert → Insert Statistic Chart → Pareto. Excel sorts the reasons from most to fewest claims and adds a cumulative-percentage line on a secondary axis that runs to 100%.
 3. Hover over the line at the second bar.
-4. To get the exact value, type =SUM(LARGE(Denials!B2:B8,{1,2}))/SUM(Denials!B2:B8) and format it as a percentage.</t>
+4. To get the exact value, type =(LARGE(Denials!B2:B8,1)+LARGE(Denials!B2:B8,2))/SUM(Denials!B2:B8) and format it as a percentage with 1 decimal place.</t>
         </is>
       </c>
       <c r="E14" cm="1" s="57">
@@ -4310,11 +4311,11 @@
       </c>
       <c r="F14" s="19" t="inlineStr">
         <is>
-          <t>Authorization Required (395 claims) and Medical Necessity (243) make up 638 of 1,142 denied claims. A Pareto chart ranks causes so a team can see the "vital few" worth fixing first. Here the first two reasons cover 55.9% of denials and the first four cover 84.3%. The built-in Pareto sorts the data for you, so the table itself can stay in any order. Cross-check with a formula: =SUM(LARGE(tblDenials[Claims],{1,2}))/SUM(tblDenials[Claims])</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="156" customHeight="1">
+          <t>Authorization Required (395 claims) and Medical Necessity (243) make up 638 of 1,142 denied claims. A Pareto chart ranks causes so a team can see the "vital few" worth fixing first. Here the first two reasons cover 55.9% of denials and the first four cover 84.3%. The built-in Pareto sorts the data for you, so the table itself can stay in any order. LARGE(range,1) and LARGE(range,2) return the largest and second-largest claim counts, which are the first two bars. The shorter cross-check formula that follows hands LARGE the array constant {1,2} (Lesson 2.5) so it returns both at once, and SUM adds them. Cross-check with a formula: =SUM(LARGE(tblDenials[Claims],{1,2}))/SUM(tblDenials[Claims])</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="171" customHeight="1">
       <c r="A15" s="18" t="inlineStr">
         <is>
           <t>11</t>
@@ -4335,7 +4336,7 @@
           <t>1. Select A4:B14 on Budget.
 2. Choose Insert → Insert Waterfall, Funnel, Stock, Surface, or Radar Chart → Waterfall (Mac: Insert → Waterfall).
 3. Click the first bar once to select the series and once more to select only that bar. Right-click it → Set as Total. Do the same for the last bar.
-4. The longest orange (Decrease) bar is the answer.</t>
+4. Find the longest bar in the Decrease color (the legend shows which color that is). Hover over it to read its Step name.</t>
         </is>
       </c>
       <c r="E15" cm="1" s="51">
@@ -4380,7 +4381,7 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="141" customHeight="1">
+    <row r="17" ht="156" customHeight="1">
       <c r="A17" s="18" t="inlineStr">
         <is>
           <t>13</t>
@@ -4388,7 +4389,7 @@
       </c>
       <c r="B17" s="19" t="inlineStr">
         <is>
-          <t>Write a formula in the yellow cell that builds this chart title from tblEDMonthly: ED visits by facility, [first month] to [last month] ([total visits] visits). Show each month as a three-letter month and year, and the total with a thousands separator. Example of the pattern: ED visits by facility, Mar 2023 to Feb 2024 (9,876 visits). Then link your line chart's title to this cell.</t>
+          <t>Write a formula in the yellow cell that builds this chart title from tblEDMonthly: ED visits by facility, [first month] to [last month] ([total visits] visits). Show each month as a three-letter month and year, and the total with a thousands separator. Example of the pattern: ED visits by facility, Mar 2023 to Feb 2024 (9,876 visits). Then link the title of your Task 2 line chart to this cell.</t>
         </is>
       </c>
       <c r="C17" s="49" t="inlineStr">
@@ -4407,7 +4408,7 @@
       </c>
       <c r="F17" s="19" t="inlineStr">
         <is>
-          <t>Build the title in a cell, because a chart title can show text or one cell reference, but not a formula. To link it, click the chart title, type = in the formula bar, click this yellow cell, and press Enter. The formula bar then shows a reference such as =Practice!$D$18. TEXT turns the dates and the total into formatted text. Without it, &amp; would join the raw serial number 45292 instead of Jan 2024. Because the formula uses tblEDMonthly, adding January 2026 as a new row updates the chart and its title together.</t>
+          <t>Build the title in a cell, because a chart title can show text or one cell reference, but not a formula. To link it, click the chart title on ED_Monthly, type = in the formula bar, click the Practice sheet tab, click this yellow cell, and press Enter. The formula bar then shows a reference such as =Practice!$D$18. TEXT turns the dates and the total into formatted text. Without it, &amp; would join the raw serial number 45292 instead of Jan 2024. Because the formula uses tblEDMonthly, adding January 2026 as a new row updates the chart and its title together.</t>
         </is>
       </c>
     </row>
@@ -4484,7 +4485,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="66" customHeight="1">
+    <row r="5" ht="96" customHeight="1">
       <c r="A5" s="18" t="inlineStr">
         <is>
           <t>B1</t>
@@ -4492,7 +4493,7 @@
       </c>
       <c r="B5" s="19" t="inlineStr">
         <is>
-          <t>On ED_Monthly, fill the yellow LWBSRate column with LWBS ÷ Total for each month and format it as a percentage. The gray cell counts the months above the 2% target. How many of the 24 months missed the target?</t>
+          <t>On ED_Monthly, fill the yellow LWBSRate column with LWBS ÷ Total for each month. The column is already formatted as a percentage. The gray cell counts the months above the 2% target. How many of the 24 months missed the target?</t>
         </is>
       </c>
       <c r="C5" s="49" t="n">
@@ -4500,7 +4501,7 @@
       </c>
       <c r="D5" s="50" t="inlineStr">
         <is>
-          <t>=F2/E2</t>
+          <t>=[@LWBS]/[@Total]</t>
         </is>
       </c>
       <c r="E5" cm="1" s="51">
@@ -4509,7 +4510,7 @@
       </c>
       <c r="F5" s="19" t="inlineStr">
         <is>
-          <t>Type =[@LWBS]/[@Total] (or =F2/E2) in G2. The Table fills the column for you. Rates make months comparable even though volume swings by 228 visits between the busiest and quietest months. 8 of the 24 months were above 2%.</t>
+          <t>Type the formula in G2 (=F2/E2 works too). [@LWBS] means "the LWBS value in this row", and the Table fills the column for you. Rates make months comparable even though volume swings by 228 visits between the busiest and quietest months. The gray cell runs COUNTIF(G2:G25,"&gt;0.02") on your column, and 8 of the 24 months were above 2%.</t>
         </is>
       </c>
     </row>
@@ -4577,7 +4578,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="216" customHeight="1">
+    <row r="8" ht="231" customHeight="1">
       <c r="A8" s="18" t="inlineStr">
         <is>
           <t>B4</t>
@@ -4594,7 +4595,7 @@
       <c r="D8" s="50" t="inlineStr">
         <is>
           <t>1. Click a DeniedCharges cell → Data → Sort Largest to Smallest.
-2. In D2 type =SUM($C$2:C2)/SUM($C$2:$C$8) and press Enter. The Table fills it down. Format the column as a percentage.
+2. In D2 type =SUM($C$2:C2)/SUM($C$2:$C$8) and press Enter. The Table fills it down, and the column is already formatted as a percentage.
 3. Select A1:A8, then Ctrl+click (Mac: ⌘+click) C1:D8, and choose Insert → Insert Combo Chart → Clustered Column – Line on Secondary Axis.
 4. Double-click the secondary axis and set Minimum 0 and Maximum 1. Optionally set the column Gap Width to about 10%.
 5. Find the first bar where the line reaches 80%.</t>
@@ -4610,7 +4611,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="156" customHeight="1">
+    <row r="9" ht="201" customHeight="1">
       <c r="A9" s="18" t="inlineStr">
         <is>
           <t>B5</t>
@@ -4637,7 +4638,7 @@
       </c>
       <c r="F9" s="19" t="inlineStr">
         <is>
-          <t>Missing Documentation denials are fewer (97 claims against 125 for Eligibility / Coverage) but larger: about $14,026 per claim against $10,083. That's why the director asked for dollars. A count Pareto ranks the work queue by volume, and a dollar Pareto ranks it by money at risk. Showing both charts side by side, with the same colors and order, lets the committee see the difference at a glance. Cross-check: =INDEX(tblDenials[DenialReason],MATCH(1,--(COUNTIF(tblDenials[DeniedCharges],"&gt;"&amp;tblDenials[DeniedCharges])&lt;COUNTIF(tblDenials[Claims],"&gt;"&amp;tblDenials[Claims])),0))</t>
+          <t>Missing Documentation denials are fewer (97 claims against 125 for Eligibility / Coverage) but larger: about $14,026 per claim against $10,083. That's why the director asked for dollars. A count Pareto ranks the work queue by volume, and a dollar Pareto ranks it by money at risk. Put the two charts side by side, at the same size, so the committee sees the swap at a glance. Cross-check (COUNTIF(range,"&gt;"&amp;range) gives each reason's rank minus 1, so MATCH finds the reason whose dollar rank beats its claim rank. In Excel 2019 or earlier, confirm it with Ctrl + Shift + Enter): =INDEX(tblDenials[DenialReason],MATCH(1,--(COUNTIF(tblDenials[DeniedCharges],"&gt;"&amp;tblDenials[DeniedCharges])&lt;COUNTIF(tblDenials[Claims],"&gt;"&amp;tblDenials[Claims])),0))</t>
         </is>
       </c>
     </row>
@@ -4678,7 +4679,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Reference versions of every chart in the lesson. Helper tables on the left feed the charts that need sorted or pre-binned data. Your colors, sizes, and fonts can differ; compare the shape and the numbers.</t>
+          <t>Reference versions of every chart in the lesson. Helper tables on the left feed the charts that need sorted or pre-binned data. Your colors, sizes, and fonts can differ, so compare the shapes and the numbers.</t>
         </is>
       </c>
     </row>
@@ -6092,7 +6093,7 @@
       </c>
       <c r="C8" s="20" t="inlineStr">
         <is>
-          <t>Excel draws the first row of a bar chart at the bottom. Fix: Format Axis → Categories in reverse order</t>
+          <t>Read the chart, not the table. Guide section 6 explains the bar order and how to fix it</t>
         </is>
       </c>
       <c r="D8" s="24" t="n"/>
@@ -6101,7 +6102,7 @@
         <v/>
       </c>
     </row>
-    <row r="9" ht="66" customHeight="1">
+    <row r="9" ht="81" customHeight="1">
       <c r="A9" s="18" t="inlineStr">
         <is>
           <t>4</t>
@@ -6109,7 +6110,7 @@
       </c>
       <c r="B9" s="19" t="inlineStr">
         <is>
-          <t>The Makeover sheet has a colleague's column chart of the same readmission rates. Its vertical axis starts at 5%, not 0%. Measured from that axis, how many times taller is the Cardiovascular bar than the Women &amp; Children bar? Round to 1 decimal place. Then fix the chart.</t>
+          <t>The Makeover sheet has a colleague's column chart of the same readmission rates. Its vertical axis starts at 5%, not 0%. Measured from that axis, how many times taller is the Cardiovascular bar than the Women &amp; Children bar? Round to 1 decimal place. Then fix the chart in place, using the checklist in Guide section 16, and add alt text.</t>
         </is>
       </c>
       <c r="C9" s="20" t="inlineStr">
@@ -6167,7 +6168,7 @@
         <v/>
       </c>
     </row>
-    <row r="12" ht="66" customHeight="1">
+    <row r="12" ht="81" customHeight="1">
       <c r="A12" s="18" t="inlineStr">
         <is>
           <t>7</t>
@@ -6180,7 +6181,7 @@
       </c>
       <c r="C12" s="20" t="inlineStr">
         <is>
-          <t>Insert → Insert Scatter (X, Y) → Scatter. Then + → Trendline → More Options → Display Equation on chart</t>
+          <t>Insert → Insert Scatter (X, Y) or Bubble Chart → Scatter. Right-click a point → Add Trendline, then tick Display Equation on chart. SLOPE takes the Y range first</t>
         </is>
       </c>
       <c r="D12" s="27" t="n"/>
@@ -6299,7 +6300,7 @@
         <v/>
       </c>
     </row>
-    <row r="18" ht="81" customHeight="1">
+    <row r="18" ht="96" customHeight="1">
       <c r="A18" s="18" t="inlineStr">
         <is>
           <t>13</t>
@@ -6307,7 +6308,7 @@
       </c>
       <c r="B18" s="19" t="inlineStr">
         <is>
-          <t>Write a formula in the yellow cell that builds this chart title from tblEDMonthly: ED visits by facility, [first month] to [last month] ([total visits] visits). Show each month as a three-letter month and year, and the total with a thousands separator. Example of the pattern: ED visits by facility, Mar 2023 to Feb 2024 (9,876 visits). Then link your line chart's title to this cell.</t>
+          <t>Write a formula in the yellow cell that builds this chart title from tblEDMonthly: ED visits by facility, [first month] to [last month] ([total visits] visits). Show each month as a three-letter month and year, and the total with a thousands separator. Example of the pattern: ED visits by facility, Mar 2023 to Feb 2024 (9,876 visits). Then link the title of your Task 2 line chart to this cell.</t>
         </is>
       </c>
       <c r="C18" s="20" t="inlineStr">

--- a/03-data-analysis/05-charts-visualization/3.5-charts-visualization.xlsx
+++ b/03-data-analysis/05-charts-visualization/3.5-charts-visualization.xlsx
@@ -240,7 +240,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="70">
+  <cellXfs count="69">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -344,44 +344,41 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
     <xf numFmtId="166" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="167" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="169" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="169" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="170" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="170" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -3305,7 +3302,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="33" customHeight="1">
+    <row r="15" ht="18" customHeight="1">
       <c r="B15" s="8" t="inlineStr">
         <is>
           <t>3. Check yourself</t>
@@ -3313,7 +3310,7 @@
       </c>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>The Check column shows ✔ Correct (green) or ✘ Not yet (red). Tasks marked 'See key' are checked by comparing with the answer key.</t>
+          <t>The Check column shows ✔ Correct (green) or ✘ Not yet (red).</t>
         </is>
       </c>
     </row>
@@ -3429,7 +3426,7 @@
       </c>
       <c r="C26" s="7" t="inlineStr">
         <is>
-          <t>Pre-filled summary formula — it reads the work you did on another sheet.</t>
+          <t>Pre-filled summary formula. It reads the work you did on another sheet, so don't type over it.</t>
         </is>
       </c>
     </row>
@@ -3453,7 +3450,7 @@
       </c>
       <c r="C28" s="7" t="inlineStr">
         <is>
-          <t>Not matching yet — check the hint and try again.</t>
+          <t>Not matching yet. Check the hint and try again.</t>
         </is>
       </c>
     </row>
@@ -3473,7 +3470,7 @@
       </c>
       <c r="C31" s="7" t="inlineStr">
         <is>
-          <t>Data: 24 rows — Excel Table 'tblEDHourly'</t>
+          <t>Data: 24 rows, in the Excel Table 'tblEDHourly'</t>
         </is>
       </c>
     </row>
@@ -3485,7 +3482,7 @@
       </c>
       <c r="C32" s="7" t="inlineStr">
         <is>
-          <t>Data: 24 rows — Excel Table 'tblEDMonthly'</t>
+          <t>Data: 24 rows, in the Excel Table 'tblEDMonthly'</t>
         </is>
       </c>
     </row>
@@ -3497,7 +3494,7 @@
       </c>
       <c r="C33" s="7" t="inlineStr">
         <is>
-          <t>Data: 8 rows — Excel Table 'tblReadmits'</t>
+          <t>Data: 8 rows, in the Excel Table 'tblReadmits'</t>
         </is>
       </c>
     </row>
@@ -3509,7 +3506,7 @@
       </c>
       <c r="C34" s="7" t="inlineStr">
         <is>
-          <t>Data: 5 rows — Excel Table 'tblPayerMix'</t>
+          <t>Data: 5 rows, in the Excel Table 'tblPayerMix'</t>
         </is>
       </c>
     </row>
@@ -3521,7 +3518,7 @@
       </c>
       <c r="C35" s="7" t="inlineStr">
         <is>
-          <t>Data: 300 rows — Excel Table 'tblStays'</t>
+          <t>Data: 300 rows, in the Excel Table 'tblStays'</t>
         </is>
       </c>
     </row>
@@ -3533,7 +3530,7 @@
       </c>
       <c r="C36" s="7" t="inlineStr">
         <is>
-          <t>Data: 7 rows — Excel Table 'tblDenials'</t>
+          <t>Data: 7 rows, in the Excel Table 'tblDenials'</t>
         </is>
       </c>
     </row>
@@ -3545,7 +3542,7 @@
       </c>
       <c r="C37" s="7" t="inlineStr">
         <is>
-          <t>Data: 10 rows — Excel Table 'tblBudget'</t>
+          <t>Data: 10 rows, in the Excel Table 'tblBudget'</t>
         </is>
       </c>
     </row>
@@ -3943,7 +3940,7 @@
     <col width="55" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="48" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
     <col width="62" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
@@ -3957,7 +3954,7 @@
     <row r="2" ht="32" customHeight="1">
       <c r="A2" s="47" t="inlineStr">
         <is>
-          <t>Spoiler alert — try every task before reading this sheet. Column C is the value the Check column compares against. Column D is a sample solution; column E is that same formula, live, proving it works.</t>
+          <t>Spoiler alert: try every task before reading this sheet. Column C is the value the Check column compares against. Column D is a sample solution, and column E recalculates a formula for it live, proving the answer.</t>
         </is>
       </c>
     </row>
@@ -4014,7 +4011,7 @@
 3. Drag the chart to the right of the table. Hover over the tallest column: the tooltip reads Series "Arrivals" Point "16:00" Value: 408.</t>
         </is>
       </c>
-      <c r="E5" cm="1" s="51">
+      <c r="E5" cm="1" s="19">
         <f t="array" ref="E5">VALUE(LEFT(_xlfn.XLOOKUP(MAX(tblEDHourly[Arrivals]),tblEDHourly[Arrivals],tblEDHourly[ArrivalHour]),2))</f>
         <v/>
       </c>
@@ -4024,7 +4021,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="141" customHeight="1">
+    <row r="6" ht="126" customHeight="1">
       <c r="A6" s="18" t="inlineStr">
         <is>
           <t>2</t>
@@ -4035,7 +4032,7 @@
           <t>On ED_Monthly, select A1:D25 (Month and the three hospitals) and insert a line chart. In which month did Cedar Ridge have its most ED visits? Type the month and year (for example, Jun 2025).</t>
         </is>
       </c>
-      <c r="C6" s="52" t="n">
+      <c r="C6" s="51" t="n">
         <v>45352</v>
       </c>
       <c r="D6" s="50" t="inlineStr">
@@ -4045,7 +4042,7 @@
 3. Hover over the highest point of the Cedar Ridge line, or click the line once and read the values in the tooltips.</t>
         </is>
       </c>
-      <c r="E6" cm="1" s="53">
+      <c r="E6" cm="1" s="52">
         <f t="array" ref="E6">_xlfn.XLOOKUP(MAX(tblEDMonthly[Cedar Ridge]),tblEDMonthly[Cedar Ridge],tblEDMonthly[Month])</f>
         <v/>
       </c>
@@ -4080,7 +4077,7 @@
 5. To fix the order, double-click the vertical (category) axis to open Format Axis, then under Axis Options tick Categories in reverse order. Set Horizontal axis crosses to At maximum category so the value axis stays at the bottom.</t>
         </is>
       </c>
-      <c r="E7" cm="1" s="51">
+      <c r="E7" cm="1" s="19">
         <f t="array" ref="E7">_xlfn.XLOOKUP(MIN(tblReadmits[ReadmitRate]),tblReadmits[ReadmitRate],tblReadmits[ServiceLine])</f>
         <v/>
       </c>
@@ -4090,7 +4087,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="261" customHeight="1">
+    <row r="8" ht="231" customHeight="1">
       <c r="A8" s="18" t="inlineStr">
         <is>
           <t>4</t>
@@ -4101,7 +4098,7 @@
           <t>The Makeover sheet has a colleague's column chart of the same readmission rates. Its vertical axis starts at 5%, not 0%. Measured from that axis, how many times taller is the Cardiovascular bar than the Women &amp; Children bar? Round to 1 decimal place. Then fix the chart in place, using the checklist in Guide section 16, and add alt text.</t>
         </is>
       </c>
-      <c r="C8" s="54" t="n">
+      <c r="C8" s="53" t="n">
         <v>9.6</v>
       </c>
       <c r="D8" s="50" t="inlineStr">
@@ -4112,7 +4109,7 @@
 4. Right-click the chart → Edit Alt Text and describe it, for example: Column chart of 2025 30-day readmission rates by service line. Cardiovascular is highest at 18.4% and Women &amp; Children lowest at 6.4%.</t>
         </is>
       </c>
-      <c r="E8" cm="1" s="55">
+      <c r="E8" cm="1" s="54">
         <f t="array" ref="E8">(MAX(tblReadmits[ReadmitRate])-0.05)/(MIN(tblReadmits[ReadmitRate])-0.05)</f>
         <v/>
       </c>
@@ -4122,7 +4119,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="186" customHeight="1">
+    <row r="9" ht="171" customHeight="1">
       <c r="A9" s="18" t="inlineStr">
         <is>
           <t>5</t>
@@ -4133,7 +4130,7 @@
           <t>On PayerMix, insert a pie chart of 2025 encounters by PayerType. Add data labels that show the Percentage (not the Value), formatted with 1 decimal place. What does the Commercial label show?</t>
         </is>
       </c>
-      <c r="C9" s="56" t="n">
+      <c r="C9" s="55" t="n">
         <v>0.3766711529834006</v>
       </c>
       <c r="D9" s="50" t="inlineStr">
@@ -4144,7 +4141,7 @@
 4. Read the Commercial slice.</t>
         </is>
       </c>
-      <c r="E9" cm="1" s="57">
+      <c r="E9" cm="1" s="56">
         <f t="array" ref="E9">_xlfn.XLOOKUP("Commercial",tblPayerMix[PayerType],tblPayerMix[Encounters])/SUM(tblPayerMix[Encounters])</f>
         <v/>
       </c>
@@ -4154,7 +4151,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="171" customHeight="1">
+    <row r="10" ht="156" customHeight="1">
       <c r="A10" s="18" t="inlineStr">
         <is>
           <t>6</t>
@@ -4176,7 +4173,7 @@
 4. Hover over the last column, labeled &gt;10.</t>
         </is>
       </c>
-      <c r="E10" cm="1" s="51">
+      <c r="E10" cm="1" s="19">
         <f t="array" ref="E10">COUNTIF(tblStays[LOSDays],"&gt;10")</f>
         <v/>
       </c>
@@ -4197,7 +4194,7 @@
           <t>On Stays, select D1:E301 (LOSDays and TotalCharges) and insert an XY scatter chart, so LOSDays is on the horizontal axis. Add a linear trendline and display its equation. By how many dollars do charges rise for each extra day in the hospital? Confirm with SLOPE and round to the nearest dollar.</t>
         </is>
       </c>
-      <c r="C11" s="58" t="n">
+      <c r="C11" s="57" t="n">
         <v>4921.959897703761</v>
       </c>
       <c r="D11" s="50" t="inlineStr">
@@ -4209,7 +4206,7 @@
 5. Confirm in the yellow cell: =SLOPE(Stays!E2:E301,Stays!D2:D301).</t>
         </is>
       </c>
-      <c r="E11" cm="1" s="59">
+      <c r="E11" cm="1" s="58">
         <f t="array" ref="E11">SLOPE(tblStays[TotalCharges],tblStays[LOSDays])</f>
         <v/>
       </c>
@@ -4219,7 +4216,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="141" customHeight="1">
+    <row r="12" ht="126" customHeight="1">
       <c r="A12" s="18" t="inlineStr">
         <is>
           <t>8</t>
@@ -4230,7 +4227,7 @@
           <t>Make a second scatter chart on Stays with AgeAtAdmit on the horizontal axis and LOSDays on the vertical axis (C1:D301). Add a linear trendline and display the R-squared value. What is R²? Confirm with RSQ and enter it to 4 decimal places.</t>
         </is>
       </c>
-      <c r="C12" s="60" t="n">
+      <c r="C12" s="59" t="n">
         <v>0.01851500698619864</v>
       </c>
       <c r="D12" s="50" t="inlineStr">
@@ -4241,7 +4238,7 @@
 4. Confirm in the yellow cell: =RSQ(Stays!D2:D301,Stays!C2:C301).</t>
         </is>
       </c>
-      <c r="E12" cm="1" s="61">
+      <c r="E12" cm="1" s="60">
         <f t="array" ref="E12">RSQ(tblStays[LOSDays],tblStays[AgeAtAdmit])</f>
         <v/>
       </c>
@@ -4251,7 +4248,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="201" customHeight="1">
+    <row r="13" ht="186" customHeight="1">
       <c r="A13" s="18" t="inlineStr">
         <is>
           <t>9</t>
@@ -4273,7 +4270,7 @@
 4. Hover over the highest point of the line.</t>
         </is>
       </c>
-      <c r="E13" cm="1" s="51">
+      <c r="E13" cm="1" s="19">
         <f t="array" ref="E13">VALUE(LEFT(_xlfn.XLOOKUP(MAX(tblEDHourly[AvgDoorToProviderMin]),tblEDHourly[AvgDoorToProviderMin],tblEDHourly[ArrivalHour]),2))</f>
         <v/>
       </c>
@@ -4294,7 +4291,7 @@
           <t>On Denials, select A1:B8 (DenialReason and Claims) and insert a Pareto chart. What cumulative percentage does the line reach at the second bar (the top two reasons together)? Enter it as a percentage to 1 decimal place.</t>
         </is>
       </c>
-      <c r="C14" s="56" t="n">
+      <c r="C14" s="55" t="n">
         <v>0.5586690017513135</v>
       </c>
       <c r="D14" s="50" t="inlineStr">
@@ -4305,7 +4302,7 @@
 4. To get the exact value, type =(LARGE(Denials!B2:B8,1)+LARGE(Denials!B2:B8,2))/SUM(Denials!B2:B8) and format it as a percentage with 1 decimal place.</t>
         </is>
       </c>
-      <c r="E14" cm="1" s="57">
+      <c r="E14" cm="1" s="56">
         <f t="array" ref="E14">SUM(LARGE(tblDenials[Claims],{1,2}))/SUM(tblDenials[Claims])</f>
         <v/>
       </c>
@@ -4339,7 +4336,7 @@
 4. Find the longest bar in the Decrease color (the legend shows which color that is). Hover over it to read its Step name.</t>
         </is>
       </c>
-      <c r="E15" cm="1" s="51">
+      <c r="E15" cm="1" s="19">
         <f t="array" ref="E15">_xlfn.XLOOKUP(MIN(tblBudget[Amount]),tblBudget[Amount],tblBudget[Step])</f>
         <v/>
       </c>
@@ -4371,7 +4368,7 @@
 4. Compare each sparkline's two end markers. To check, compare row 25 with row 2.</t>
         </is>
       </c>
-      <c r="E16" cm="1" s="51">
+      <c r="E16" cm="1" s="19">
         <f t="array" ref="E16">SUMPRODUCT(--(ED_Monthly!$B$25:$D$25&gt;ED_Monthly!$B$2:$D$2))</f>
         <v/>
       </c>
@@ -4402,7 +4399,7 @@
           <t>="ED visits by facility, "&amp;TEXT(MIN(tblEDMonthly[Month]),"mmm yyyy")&amp;" to "&amp;TEXT(MAX(tblEDMonthly[Month]),"mmm yyyy")&amp;" ("&amp;TEXT(SUM(tblEDMonthly[Total]),"#,##0")&amp;" visits)"</t>
         </is>
       </c>
-      <c r="E17" cm="1" s="51">
+      <c r="E17" cm="1" s="19">
         <f t="array" ref="E17">"ED visits by facility, "&amp;TEXT(MIN(tblEDMonthly[Month]),"mmm yyyy")&amp;" to "&amp;TEXT(MAX(tblEDMonthly[Month]),"mmm yyyy")&amp;" ("&amp;TEXT(SUM(tblEDMonthly[Total]),"#,##0")&amp;" visits)"</f>
         <v/>
       </c>
@@ -4435,7 +4432,7 @@
     <col width="55" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="48" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
     <col width="62" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
@@ -4449,7 +4446,7 @@
     <row r="2" ht="32" customHeight="1">
       <c r="A2" s="47" t="inlineStr">
         <is>
-          <t>Spoiler alert — try every task before reading this sheet. Column C is the value the Check column compares against. Column D is a sample solution; column E is that same formula, live, proving it works.</t>
+          <t>Spoiler alert: try every task before reading this sheet. Column C is the value the Check column compares against. Column D is a sample solution, and column E recalculates a formula for it live, proving the answer.</t>
         </is>
       </c>
     </row>
@@ -4504,7 +4501,7 @@
           <t>=[@LWBS]/[@Total]</t>
         </is>
       </c>
-      <c r="E5" cm="1" s="51">
+      <c r="E5" cm="1" s="19">
         <f t="array" ref="E5">SUMPRODUCT(--(tblEDMonthly[LWBS]/tblEDMonthly[Total]&gt;0.02))</f>
         <v/>
       </c>
@@ -4514,7 +4511,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="171" customHeight="1">
+    <row r="6" ht="141" customHeight="1">
       <c r="A6" s="18" t="inlineStr">
         <is>
           <t>B2</t>
@@ -4525,7 +4522,7 @@
           <t>Build a combo chart on ED_Monthly with Total as clustered columns and LWBSRate as a line on the secondary axis (select Month, then Ctrl+click or ⌘+click Total and LWBSRate). Which month had the highest LWBS rate? Type the month and year.</t>
         </is>
       </c>
-      <c r="C6" s="52" t="n">
+      <c r="C6" s="51" t="n">
         <v>45536</v>
       </c>
       <c r="D6" s="50" t="inlineStr">
@@ -4536,7 +4533,7 @@
 4. Hover over the highest point of the line.</t>
         </is>
       </c>
-      <c r="E6" cm="1" s="53">
+      <c r="E6" cm="1" s="52">
         <f t="array" ref="E6">_xlfn.XLOOKUP(MAX(tblEDMonthly[LWBS]/tblEDMonthly[Total]),tblEDMonthly[LWBS]/tblEDMonthly[Total],tblEDMonthly[Month])</f>
         <v/>
       </c>
@@ -4546,7 +4543,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="156" customHeight="1">
+    <row r="7" ht="141" customHeight="1">
       <c r="A7" s="18" t="inlineStr">
         <is>
           <t>B3</t>
@@ -4557,7 +4554,7 @@
           <t>Test the director's theory with a scatter chart of Total (horizontal axis) against LWBSRate (vertical axis), with a linear trendline and its R². What is R²? Enter it to 3 decimal places.</t>
         </is>
       </c>
-      <c r="C7" s="62" t="n">
+      <c r="C7" s="61" t="n">
         <v>0.1209547597763709</v>
       </c>
       <c r="D7" s="50" t="inlineStr">
@@ -4568,7 +4565,7 @@
 4. Confirm: =RSQ(ED_Monthly!G2:G25,ED_Monthly!E2:E25).</t>
         </is>
       </c>
-      <c r="E7" cm="1" s="63">
+      <c r="E7" cm="1" s="62">
         <f t="array" ref="E7">RSQ(tblEDMonthly[LWBS]/tblEDMonthly[Total],tblEDMonthly[Total])</f>
         <v/>
       </c>
@@ -4601,7 +4598,7 @@
 5. Find the first bar where the line reaches 80%.</t>
         </is>
       </c>
-      <c r="E8" cm="1" s="51">
+      <c r="E8" cm="1" s="19">
         <f t="array" ref="E8">SUMPRODUCT(--(SUMIF(tblDenials[DeniedCharges],"&gt;="&amp;tblDenials[DeniedCharges])&lt;0.8*SUM(tblDenials[DeniedCharges])))+1</f>
         <v/>
       </c>
@@ -4632,7 +4629,7 @@
           <t>Read the bar order in both charts. By claims, Missing Documentation is number 5, and by denied charges it's number 4, so it swaps places with Eligibility / Coverage.</t>
         </is>
       </c>
-      <c r="E9" cm="1" s="51">
+      <c r="E9" cm="1" s="19">
         <f t="array" ref="E9">INDEX(tblDenials[DenialReason],MATCH(1,--(COUNTIF(tblDenials[DeniedCharges],"&gt;"&amp;tblDenials[DeniedCharges])&lt;COUNTIF(tblDenials[Claims],"&gt;"&amp;tblDenials[Claims])),0))</f>
         <v/>
       </c>
@@ -4684,14 +4681,14 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="64" t="inlineStr">
+      <c r="A4" s="63" t="inlineStr">
         <is>
           <t>Task 1 · Column chart: 2025 ED arrivals by hour of day</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="65" t="inlineStr">
+      <c r="A5" s="64" t="inlineStr">
         <is>
           <t>Data</t>
         </is>
@@ -4705,19 +4702,19 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="64" t="inlineStr">
+      <c r="A24" s="63" t="inlineStr">
         <is>
           <t>Tasks 2 &amp; 13 · Line chart: monthly ED visits by hospital (title linked to Task 13's cell)</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="65" t="inlineStr">
+      <c r="A25" s="64" t="inlineStr">
         <is>
           <t>Data</t>
         </is>
       </c>
-      <c r="B25" s="66" t="inlineStr">
+      <c r="B25" s="65" t="inlineStr">
         <is>
           <t>Title text</t>
         </is>
@@ -4736,19 +4733,19 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="64" t="inlineStr">
+      <c r="A44" s="63" t="inlineStr">
         <is>
           <t>Task 3 · Bar chart: readmission rate by service line (sorted, categories reversed)</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="65" t="inlineStr">
+      <c r="A45" s="64" t="inlineStr">
         <is>
           <t>ServiceLine</t>
         </is>
       </c>
-      <c r="B45" s="66" t="inlineStr">
+      <c r="B45" s="65" t="inlineStr">
         <is>
           <t>ReadmitRate</t>
         </is>
@@ -4835,19 +4832,19 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="64" t="inlineStr">
+      <c r="A64" s="63" t="inlineStr">
         <is>
           <t>Task 4 · Makeover fixed: axis from 0%, one color, labels instead of a legend</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="65" t="inlineStr">
+      <c r="A65" s="64" t="inlineStr">
         <is>
           <t>ServiceLine</t>
         </is>
       </c>
-      <c r="B65" s="66" t="inlineStr">
+      <c r="B65" s="65" t="inlineStr">
         <is>
           <t>ReadmitRate</t>
         </is>
@@ -4934,14 +4931,14 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="64" t="inlineStr">
+      <c r="A84" s="63" t="inlineStr">
         <is>
           <t>Task 5 · Pie chart: 2025 encounters by payer type (Percentage labels, 1 decimal)</t>
         </is>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="65" t="inlineStr">
+      <c r="A85" s="64" t="inlineStr">
         <is>
           <t>Data</t>
         </is>
@@ -4955,19 +4952,19 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="64" t="inlineStr">
+      <c r="A104" s="63" t="inlineStr">
         <is>
           <t>Task 6 · Histogram of LOSDays: bin width 1, underflow 1, overflow 10 (classic column version)</t>
         </is>
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="65" t="inlineStr">
+      <c r="A105" s="64" t="inlineStr">
         <is>
           <t>Bin (days)</t>
         </is>
       </c>
-      <c r="B105" s="66" t="inlineStr">
+      <c r="B105" s="65" t="inlineStr">
         <is>
           <t>Stays</t>
         </is>
@@ -5084,24 +5081,24 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="64" t="inlineStr">
+      <c r="A124" s="63" t="inlineStr">
         <is>
           <t>Task 7 · Scatter: LOSDays (x) vs TotalCharges (y), linear trendline</t>
         </is>
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="65" t="inlineStr">
+      <c r="A125" s="64" t="inlineStr">
         <is>
           <t>SLOPE</t>
         </is>
       </c>
-      <c r="B125" s="66" t="inlineStr">
+      <c r="B125" s="65" t="inlineStr">
         <is>
           <t>INTERCEPT</t>
         </is>
       </c>
-      <c r="C125" s="66" t="inlineStr">
+      <c r="C125" s="65" t="inlineStr">
         <is>
           <t>R²</t>
         </is>
@@ -5114,54 +5111,54 @@
       <c r="B126" s="39" t="n">
         <v>9225.06444314586</v>
       </c>
-      <c r="C126" s="67" t="n">
+      <c r="C126" s="66" t="n">
         <v>0.3100799609472633</v>
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="64" t="inlineStr">
+      <c r="A144" s="63" t="inlineStr">
         <is>
           <t>Task 8 · Scatter: AgeAtAdmit (x) vs LOSDays (y), linear trendline</t>
         </is>
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="65" t="inlineStr">
+      <c r="A145" s="64" t="inlineStr">
         <is>
           <t>SLOPE</t>
         </is>
       </c>
-      <c r="B145" s="66" t="inlineStr">
+      <c r="B145" s="65" t="inlineStr">
         <is>
           <t>INTERCEPT</t>
         </is>
       </c>
-      <c r="C145" s="66" t="inlineStr">
+      <c r="C145" s="65" t="inlineStr">
         <is>
           <t>R²</t>
         </is>
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="67" t="n">
+      <c r="A146" s="66" t="n">
         <v>0.01685011370419272</v>
       </c>
-      <c r="B146" s="67" t="n">
+      <c r="B146" s="66" t="n">
         <v>3.605362337692334</v>
       </c>
-      <c r="C146" s="67" t="n">
+      <c r="C146" s="66" t="n">
         <v>0.01851500698619864</v>
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="64" t="inlineStr">
+      <c r="A164" s="63" t="inlineStr">
         <is>
           <t>Task 9 · Combo: arrivals (columns) + average door-to-provider minutes (line, secondary axis)</t>
         </is>
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="65" t="inlineStr">
+      <c r="A165" s="64" t="inlineStr">
         <is>
           <t>Data</t>
         </is>
@@ -5175,24 +5172,24 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="64" t="inlineStr">
+      <c r="A184" s="63" t="inlineStr">
         <is>
           <t>Task 10 · Pareto by claim count (sorted columns + cumulative % line)</t>
         </is>
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="65" t="inlineStr">
+      <c r="A185" s="64" t="inlineStr">
         <is>
           <t>DenialReason</t>
         </is>
       </c>
-      <c r="B185" s="66" t="inlineStr">
+      <c r="B185" s="65" t="inlineStr">
         <is>
           <t>Claims</t>
         </is>
       </c>
-      <c r="C185" s="66" t="inlineStr">
+      <c r="C185" s="65" t="inlineStr">
         <is>
           <t>Cumulative %</t>
         </is>
@@ -5290,34 +5287,34 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="64" t="inlineStr">
+      <c r="A204" s="63" t="inlineStr">
         <is>
           <t>Task 11 · Waterfall (classic stacked-column version; Base series has no fill)</t>
         </is>
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="65" t="inlineStr">
+      <c r="A205" s="64" t="inlineStr">
         <is>
           <t>Step</t>
         </is>
       </c>
-      <c r="B205" s="66" t="inlineStr">
+      <c r="B205" s="65" t="inlineStr">
         <is>
           <t>Base</t>
         </is>
       </c>
-      <c r="C205" s="66" t="inlineStr">
+      <c r="C205" s="65" t="inlineStr">
         <is>
           <t>Increase</t>
         </is>
       </c>
-      <c r="D205" s="66" t="inlineStr">
+      <c r="D205" s="65" t="inlineStr">
         <is>
           <t>Decrease</t>
         </is>
       </c>
-      <c r="E205" s="66" t="inlineStr">
+      <c r="E205" s="65" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
@@ -5514,14 +5511,14 @@
       </c>
     </row>
     <row r="224">
-      <c r="A224" s="64" t="inlineStr">
+      <c r="A224" s="63" t="inlineStr">
         <is>
           <t>Task 12 · Sparklines</t>
         </is>
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="65" t="inlineStr">
+      <c r="A225" s="64" t="inlineStr">
         <is>
           <t>Expected result</t>
         </is>
@@ -5556,312 +5553,312 @@
       </c>
     </row>
     <row r="231">
-      <c r="A231" s="64" t="inlineStr">
+      <c r="A231" s="63" t="inlineStr">
         <is>
           <t>Bonus B2 · Combo: monthly ED visits (columns) + LWBS rate (line, secondary axis)</t>
         </is>
       </c>
     </row>
     <row r="232">
-      <c r="A232" s="65" t="inlineStr">
+      <c r="A232" s="64" t="inlineStr">
         <is>
           <t>Month</t>
         </is>
       </c>
-      <c r="B232" s="66" t="inlineStr">
+      <c r="B232" s="65" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="C232" s="66" t="inlineStr">
+      <c r="C232" s="65" t="inlineStr">
         <is>
           <t>LWBS rate</t>
         </is>
       </c>
     </row>
     <row r="233">
-      <c r="A233" s="68" t="n">
+      <c r="A233" s="67" t="n">
         <v>45292</v>
       </c>
       <c r="B233" s="30" t="n">
         <v>580</v>
       </c>
-      <c r="C233" s="69" t="n">
+      <c r="C233" s="68" t="n">
         <v>0.02586206896551724</v>
       </c>
     </row>
     <row r="234">
-      <c r="A234" s="68" t="n">
+      <c r="A234" s="67" t="n">
         <v>45323</v>
       </c>
       <c r="B234" s="30" t="n">
         <v>586</v>
       </c>
-      <c r="C234" s="69" t="n">
+      <c r="C234" s="68" t="n">
         <v>0.03583617747440273</v>
       </c>
     </row>
     <row r="235">
-      <c r="A235" s="68" t="n">
+      <c r="A235" s="67" t="n">
         <v>45352</v>
       </c>
       <c r="B235" s="30" t="n">
         <v>579</v>
       </c>
-      <c r="C235" s="69" t="n">
+      <c r="C235" s="68" t="n">
         <v>0.02417962003454232</v>
       </c>
     </row>
     <row r="236">
-      <c r="A236" s="68" t="n">
+      <c r="A236" s="67" t="n">
         <v>45383</v>
       </c>
       <c r="B236" s="30" t="n">
         <v>466</v>
       </c>
-      <c r="C236" s="69" t="n">
+      <c r="C236" s="68" t="n">
         <v>0.02145922746781116</v>
       </c>
     </row>
     <row r="237">
-      <c r="A237" s="68" t="n">
+      <c r="A237" s="67" t="n">
         <v>45413</v>
       </c>
       <c r="B237" s="30" t="n">
         <v>477</v>
       </c>
-      <c r="C237" s="69" t="n">
+      <c r="C237" s="68" t="n">
         <v>0.01886792452830189</v>
       </c>
     </row>
     <row r="238">
-      <c r="A238" s="68" t="n">
+      <c r="A238" s="67" t="n">
         <v>45444</v>
       </c>
       <c r="B238" s="30" t="n">
         <v>422</v>
       </c>
-      <c r="C238" s="69" t="n">
+      <c r="C238" s="68" t="n">
         <v>0.007109004739336493</v>
       </c>
     </row>
     <row r="239">
-      <c r="A239" s="68" t="n">
+      <c r="A239" s="67" t="n">
         <v>45474</v>
       </c>
       <c r="B239" s="30" t="n">
         <v>444</v>
       </c>
-      <c r="C239" s="69" t="n">
+      <c r="C239" s="68" t="n">
         <v>0.01576576576576576</v>
       </c>
     </row>
     <row r="240">
-      <c r="A240" s="68" t="n">
+      <c r="A240" s="67" t="n">
         <v>45505</v>
       </c>
       <c r="B240" s="30" t="n">
         <v>469</v>
       </c>
-      <c r="C240" s="69" t="n">
+      <c r="C240" s="68" t="n">
         <v>0.01918976545842218</v>
       </c>
     </row>
     <row r="241">
-      <c r="A241" s="68" t="n">
+      <c r="A241" s="67" t="n">
         <v>45536</v>
       </c>
       <c r="B241" s="30" t="n">
         <v>403</v>
       </c>
-      <c r="C241" s="69" t="n">
+      <c r="C241" s="68" t="n">
         <v>0.03722084367245657</v>
       </c>
     </row>
     <row r="242">
-      <c r="A242" s="68" t="n">
+      <c r="A242" s="67" t="n">
         <v>45566</v>
       </c>
       <c r="B242" s="30" t="n">
         <v>466</v>
       </c>
-      <c r="C242" s="69" t="n">
+      <c r="C242" s="68" t="n">
         <v>0.01716738197424893</v>
       </c>
     </row>
     <row r="243">
-      <c r="A243" s="68" t="n">
+      <c r="A243" s="67" t="n">
         <v>45597</v>
       </c>
       <c r="B243" s="30" t="n">
         <v>562</v>
       </c>
-      <c r="C243" s="69" t="n">
+      <c r="C243" s="68" t="n">
         <v>0.01423487544483986</v>
       </c>
     </row>
     <row r="244">
-      <c r="A244" s="68" t="n">
+      <c r="A244" s="67" t="n">
         <v>45627</v>
       </c>
       <c r="B244" s="30" t="n">
         <v>621</v>
       </c>
-      <c r="C244" s="69" t="n">
+      <c r="C244" s="68" t="n">
         <v>0.02898550724637681</v>
       </c>
     </row>
     <row r="245">
-      <c r="A245" s="68" t="n">
+      <c r="A245" s="67" t="n">
         <v>45658</v>
       </c>
       <c r="B245" s="30" t="n">
         <v>631</v>
       </c>
-      <c r="C245" s="69" t="n">
+      <c r="C245" s="68" t="n">
         <v>0.01743264659270998</v>
       </c>
     </row>
     <row r="246">
-      <c r="A246" s="68" t="n">
+      <c r="A246" s="67" t="n">
         <v>45689</v>
       </c>
       <c r="B246" s="30" t="n">
         <v>572</v>
       </c>
-      <c r="C246" s="69" t="n">
+      <c r="C246" s="68" t="n">
         <v>0.02097902097902098</v>
       </c>
     </row>
     <row r="247">
-      <c r="A247" s="68" t="n">
+      <c r="A247" s="67" t="n">
         <v>45717</v>
       </c>
       <c r="B247" s="30" t="n">
         <v>546</v>
       </c>
-      <c r="C247" s="69" t="n">
+      <c r="C247" s="68" t="n">
         <v>0.01282051282051282</v>
       </c>
     </row>
     <row r="248">
-      <c r="A248" s="68" t="n">
+      <c r="A248" s="67" t="n">
         <v>45748</v>
       </c>
       <c r="B248" s="30" t="n">
         <v>436</v>
       </c>
-      <c r="C248" s="69" t="n">
+      <c r="C248" s="68" t="n">
         <v>0.01376146788990826</v>
       </c>
     </row>
     <row r="249">
-      <c r="A249" s="68" t="n">
+      <c r="A249" s="67" t="n">
         <v>45778</v>
       </c>
       <c r="B249" s="30" t="n">
         <v>499</v>
       </c>
-      <c r="C249" s="69" t="n">
+      <c r="C249" s="68" t="n">
         <v>0.01002004008016032</v>
       </c>
     </row>
     <row r="250">
-      <c r="A250" s="68" t="n">
+      <c r="A250" s="67" t="n">
         <v>45809</v>
       </c>
       <c r="B250" s="30" t="n">
         <v>513</v>
       </c>
-      <c r="C250" s="69" t="n">
+      <c r="C250" s="68" t="n">
         <v>0.01364522417153996</v>
       </c>
     </row>
     <row r="251">
-      <c r="A251" s="68" t="n">
+      <c r="A251" s="67" t="n">
         <v>45839</v>
       </c>
       <c r="B251" s="30" t="n">
         <v>499</v>
       </c>
-      <c r="C251" s="69" t="n">
+      <c r="C251" s="68" t="n">
         <v>0.01402805611222445</v>
       </c>
     </row>
     <row r="252">
-      <c r="A252" s="68" t="n">
+      <c r="A252" s="67" t="n">
         <v>45870</v>
       </c>
       <c r="B252" s="30" t="n">
         <v>443</v>
       </c>
-      <c r="C252" s="69" t="n">
+      <c r="C252" s="68" t="n">
         <v>0.01805869074492099</v>
       </c>
     </row>
     <row r="253">
-      <c r="A253" s="68" t="n">
+      <c r="A253" s="67" t="n">
         <v>45901</v>
       </c>
       <c r="B253" s="30" t="n">
         <v>450</v>
       </c>
-      <c r="C253" s="69" t="n">
+      <c r="C253" s="68" t="n">
         <v>0.006666666666666667</v>
       </c>
     </row>
     <row r="254">
-      <c r="A254" s="68" t="n">
+      <c r="A254" s="67" t="n">
         <v>45931</v>
       </c>
       <c r="B254" s="30" t="n">
         <v>511</v>
       </c>
-      <c r="C254" s="69" t="n">
+      <c r="C254" s="68" t="n">
         <v>0.0136986301369863</v>
       </c>
     </row>
     <row r="255">
-      <c r="A255" s="68" t="n">
+      <c r="A255" s="67" t="n">
         <v>45962</v>
       </c>
       <c r="B255" s="30" t="n">
         <v>522</v>
       </c>
-      <c r="C255" s="69" t="n">
+      <c r="C255" s="68" t="n">
         <v>0.01532567049808429</v>
       </c>
     </row>
     <row r="256">
-      <c r="A256" s="68" t="n">
+      <c r="A256" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="B256" s="30" t="n">
         <v>595</v>
       </c>
-      <c r="C256" s="69" t="n">
+      <c r="C256" s="68" t="n">
         <v>0.0319327731092437</v>
       </c>
     </row>
     <row r="261">
-      <c r="A261" s="64" t="inlineStr">
+      <c r="A261" s="63" t="inlineStr">
         <is>
           <t>Bonus B4–B5 · Manual Pareto by DeniedCharges</t>
         </is>
       </c>
     </row>
     <row r="262">
-      <c r="A262" s="65" t="inlineStr">
+      <c r="A262" s="64" t="inlineStr">
         <is>
           <t>DenialReason</t>
         </is>
       </c>
-      <c r="B262" s="66" t="inlineStr">
+      <c r="B262" s="65" t="inlineStr">
         <is>
           <t>DeniedCharges</t>
         </is>
       </c>
-      <c r="C262" s="66" t="inlineStr">
+      <c r="C262" s="65" t="inlineStr">
         <is>
           <t>CumulativePct</t>
         </is>

--- a/03-data-analysis/05-charts-visualization/3.5-charts-visualization.xlsx
+++ b/03-data-analysis/05-charts-visualization/3.5-charts-visualization.xlsx
@@ -3185,7 +3185,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:C39"/>
+  <dimension ref="B2:C41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -3210,7 +3210,7 @@
     <row r="4">
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Intermediate  ·  about 55 minutes  ·  Bluestone Health System (fictional)</t>
+          <t>Intermediate  ·  about 135 minutes  ·  Bluestone Health System (fictional)</t>
         </is>
       </c>
     </row>
@@ -3465,106 +3465,130 @@
     <row r="31" ht="18" customHeight="1">
       <c r="B31" s="8" t="inlineStr">
         <is>
-          <t>ED_Hourly</t>
+          <t>Practice</t>
         </is>
       </c>
       <c r="C31" s="7" t="inlineStr">
         <is>
-          <t>Data: 24 rows, in the Excel Table 'tblEDHourly'</t>
+          <t>13 practice tasks, each with a Check cell.</t>
         </is>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
       <c r="B32" s="8" t="inlineStr">
         <is>
-          <t>ED_Monthly</t>
+          <t>ED_Hourly</t>
         </is>
       </c>
       <c r="C32" s="7" t="inlineStr">
         <is>
-          <t>Data: 24 rows, in the Excel Table 'tblEDMonthly'</t>
+          <t>Data: 24 rows, in the Excel Table 'tblEDHourly'</t>
         </is>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
       <c r="B33" s="8" t="inlineStr">
         <is>
-          <t>Readmits</t>
+          <t>ED_Monthly</t>
         </is>
       </c>
       <c r="C33" s="7" t="inlineStr">
         <is>
-          <t>Data: 8 rows, in the Excel Table 'tblReadmits'</t>
+          <t>Data: 24 rows, in the Excel Table 'tblEDMonthly'</t>
         </is>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
       <c r="B34" s="8" t="inlineStr">
         <is>
-          <t>PayerMix</t>
+          <t>Readmits</t>
         </is>
       </c>
       <c r="C34" s="7" t="inlineStr">
         <is>
-          <t>Data: 5 rows, in the Excel Table 'tblPayerMix'</t>
+          <t>Data: 8 rows, in the Excel Table 'tblReadmits'</t>
         </is>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
       <c r="B35" s="8" t="inlineStr">
         <is>
-          <t>Stays</t>
+          <t>PayerMix</t>
         </is>
       </c>
       <c r="C35" s="7" t="inlineStr">
         <is>
-          <t>Data: 300 rows, in the Excel Table 'tblStays'</t>
+          <t>Data: 5 rows, in the Excel Table 'tblPayerMix'</t>
         </is>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1">
       <c r="B36" s="8" t="inlineStr">
         <is>
-          <t>Denials</t>
+          <t>Stays</t>
         </is>
       </c>
       <c r="C36" s="7" t="inlineStr">
         <is>
-          <t>Data: 7 rows, in the Excel Table 'tblDenials'</t>
+          <t>Data: 300 rows, in the Excel Table 'tblStays'</t>
         </is>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1">
       <c r="B37" s="8" t="inlineStr">
         <is>
+          <t>Denials</t>
+        </is>
+      </c>
+      <c r="C37" s="7" t="inlineStr">
+        <is>
+          <t>Data: 7 rows, in the Excel Table 'tblDenials'</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="18" customHeight="1">
+      <c r="B38" s="8" t="inlineStr">
+        <is>
           <t>Budget</t>
         </is>
       </c>
-      <c r="C37" s="7" t="inlineStr">
+      <c r="C38" s="7" t="inlineStr">
         <is>
           <t>Data: 10 rows, in the Excel Table 'tblBudget'</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="78" customHeight="1">
-      <c r="B38" s="8" t="inlineStr">
-        <is>
-          <t>About the data</t>
-        </is>
-      </c>
-      <c r="C38" s="7" t="inlineStr">
-        <is>
-          <t>Bluestone Health System, pre-summarized for charting: monthly ED visits by hospital with counts of patients who left without being seen (LWBS), Jan 2024 – Dec 2025, 2025 ED arrivals and average door-to-provider minutes by hour of day, 2025 readmission rates by service line, 2025 payer mix, a sample of 300 of the 2,859 inpatient stays that began in 2025, 2025 claim denials by reason, and 4 West's FY2025 budget-to-actual margin bridge.</t>
         </is>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
       <c r="B39" s="8" t="inlineStr">
         <is>
+          <t>Bonus</t>
+        </is>
+      </c>
+      <c r="C39" s="7" t="inlineStr">
+        <is>
+          <t>The bonus challenge (5 parts).</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="78" customHeight="1">
+      <c r="B40" s="8" t="inlineStr">
+        <is>
+          <t>About the data</t>
+        </is>
+      </c>
+      <c r="C40" s="7" t="inlineStr">
+        <is>
+          <t>Bluestone Health System, pre-summarized for charting: monthly ED visits by hospital with counts of patients who left without being seen (LWBS), Jan 2024 – Dec 2025, 2025 ED arrivals and average door-to-provider minutes by hour of day, 2025 readmission rates by service line, 2025 payer mix, a sample of 300 of the 2,859 inpatient stays that began in 2025, 2025 claim denials by reason, and 4 West's FY2025 budget-to-actual margin bridge.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="18" customHeight="1">
+      <c r="B41" s="8" t="inlineStr">
+        <is>
           <t>Disclaimer</t>
         </is>
       </c>
-      <c r="C39" s="7" t="inlineStr">
+      <c r="C41" s="7" t="inlineStr">
         <is>
           <t>All people, places, and numbers are synthetic and fictional. Not clinical guidance.</t>
         </is>
@@ -4604,7 +4628,7 @@
       </c>
       <c r="F8" s="19" t="inlineStr">
         <is>
-          <t>Cumulative shares by dollars: Authorization Required 36.1%, Medical Necessity 59.4%, Coding Error 76.3%, Missing Documentation 86.1%, Eligibility / Coverage 95.1%, Timely Filing 97.9%, Duplicate Claim 100.0%. The line first passes 80% at reason 4, so 4 of the 7 reasons hold 86.1% of the $13,906,332 at risk. The mixed reference $C$2:C2 keeps its start fixed while its end moves down one row at a time (Lesson 1.5). Building a Pareto by hand takes longer than the built-in chart, but it works in every Excel version and lets you add an 80% reference line or label the cut-off. Cross-check (counts the reasons whose running share is still below 80%, then adds one): =SUMPRODUCT(--(SUMIF(tblDenials[DeniedCharges],"&gt;="&amp;tblDenials[DeniedCharges])&lt;0.8*SUM(tblDenials[DeniedCharges])))+1</t>
+          <t>Cumulative shares by dollars: Authorization Required 36.1%, Medical Necessity 59.4%, Coding Error 76.3%, Missing Documentation 86.1%, Eligibility / Coverage 95.1%, Timely Filing 97.9%, Duplicate Claim 100.0%. The line first passes 80% at reason 4, so 4 of the 7 reasons hold 86.1% of the $13,906,332 at risk. The expanding range $C$2:C2 (Lesson 3.3) has an absolute start and a relative end (Lesson 1.5), so its start stays fixed while its end moves down one row at a time. Building a Pareto by hand takes longer than the built-in chart, but it works in every Excel version and lets you add an 80% reference line or label the cut-off. Cross-check (counts the reasons whose running share is still below 80%, then adds one): =SUMPRODUCT(--(SUMIF(tblDenials[DeniedCharges],"&gt;="&amp;tblDenials[DeniedCharges])&lt;0.8*SUM(tblDenials[DeniedCharges])))+1</t>
         </is>
       </c>
     </row>

--- a/03-data-analysis/05-charts-visualization/3.5-charts-visualization.xlsx
+++ b/03-data-analysis/05-charts-visualization/3.5-charts-visualization.xlsx
@@ -3290,7 +3290,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="18" customHeight="1">
+    <row r="14" ht="33" customHeight="1">
       <c r="B14" s="8" t="inlineStr">
         <is>
           <t>2. Practice</t>
@@ -3298,7 +3298,7 @@
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t>Go to the 'Practice' sheet. Type a formula or value into each yellow cell.</t>
+          <t>Go to the 'Practice' sheet. Build each chart on the sheet the task names, then type the number or name it shows into the task's yellow cell. Task 13 asks for a formula.</t>
         </is>
       </c>
     </row>
@@ -3350,7 +3350,7 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="18" customHeight="1">
+    <row r="19" ht="48" customHeight="1">
       <c r="B19" s="8" t="inlineStr">
         <is>
           <t>Note</t>
@@ -3358,11 +3358,11 @@
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
-          <t>The Makeover sheet holds a deliberately misleading chart for Task 4. Fix it in place.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="48" customHeight="1">
+          <t>The hidden 'Chart Key' sheet shows a reference version of every chart. Unhide it the same way as the Answer Key. It draws the histogram, Pareto, and waterfall the classic way (column charts with helper data), so they look slightly different from Excel 2016's built-in versions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="18" customHeight="1">
       <c r="B20" s="8" t="inlineStr">
         <is>
           <t>Note</t>
@@ -3370,11 +3370,11 @@
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
-          <t>The hidden 'Chart Key' sheet shows a reference version of every chart. Unhide it the same way as the Answer Key. It draws the histogram, Pareto, and waterfall the classic way (column charts with helper data), so they look slightly different from Excel 2016's built-in versions.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="18" customHeight="1">
+          <t>Histogram, Pareto, and waterfall charts need Excel 2016 or later (Windows or Mac) or Microsoft 365.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="48" customHeight="1">
       <c r="B21" s="8" t="inlineStr">
         <is>
           <t>Note</t>
@@ -3382,131 +3382,131 @@
       </c>
       <c r="C21" s="7" t="inlineStr">
         <is>
-          <t>Histogram, Pareto, and waterfall charts need Excel 2016 or later (Windows or Mac) or Microsoft 365.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="48" customHeight="1">
-      <c r="B22" s="8" t="inlineStr">
-        <is>
-          <t>Note</t>
-        </is>
-      </c>
-      <c r="C22" s="7" t="inlineStr">
-        <is>
           <t>On the Stays sheet, LOSDays is the exact length of stay (discharge time minus admit time, in days, rounded to 1 decimal place), so it can differ slightly from the count of midnights used in Lesson 3.4.</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="B24" s="4" t="inlineStr">
+    <row r="23">
+      <c r="B23" s="4" t="inlineStr">
         <is>
           <t>Color legend</t>
         </is>
       </c>
-      <c r="C24" s="5" t="n"/>
+      <c r="C23" s="5" t="n"/>
+    </row>
+    <row r="24" ht="18" customHeight="1">
+      <c r="B24" s="9" t="inlineStr">
+        <is>
+          <t>Yellow cell</t>
+        </is>
+      </c>
+      <c r="C24" s="7" t="inlineStr">
+        <is>
+          <t>Your answer goes here.</t>
+        </is>
+      </c>
     </row>
     <row r="25" ht="18" customHeight="1">
-      <c r="B25" s="9" t="inlineStr">
-        <is>
-          <t>Yellow cell</t>
+      <c r="B25" s="10" t="inlineStr">
+        <is>
+          <t>Gray cell</t>
         </is>
       </c>
       <c r="C25" s="7" t="inlineStr">
         <is>
-          <t>Your answer goes here.</t>
+          <t>Pre-filled summary formula. It reads the work you did on another sheet, so don't type over it.</t>
         </is>
       </c>
     </row>
     <row r="26" ht="18" customHeight="1">
-      <c r="B26" s="10" t="inlineStr">
-        <is>
-          <t>Gray cell</t>
+      <c r="B26" s="11" t="inlineStr">
+        <is>
+          <t>✔ Correct</t>
         </is>
       </c>
       <c r="C26" s="7" t="inlineStr">
         <is>
-          <t>Pre-filled summary formula. It reads the work you did on another sheet, so don't type over it.</t>
+          <t>Your answer matches the key.</t>
         </is>
       </c>
     </row>
     <row r="27" ht="18" customHeight="1">
-      <c r="B27" s="11" t="inlineStr">
-        <is>
-          <t>✔ Correct</t>
+      <c r="B27" s="12" t="inlineStr">
+        <is>
+          <t>✘ Not yet</t>
         </is>
       </c>
       <c r="C27" s="7" t="inlineStr">
         <is>
-          <t>Your answer matches the key.</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="18" customHeight="1">
-      <c r="B28" s="12" t="inlineStr">
-        <is>
-          <t>✘ Not yet</t>
-        </is>
-      </c>
-      <c r="C28" s="7" t="inlineStr">
-        <is>
           <t>Not matching yet. Check the hint and try again.</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="B30" s="4" t="inlineStr">
+    <row r="29">
+      <c r="B29" s="4" t="inlineStr">
         <is>
           <t>Sheets in this workbook</t>
         </is>
       </c>
-      <c r="C30" s="5" t="n"/>
+      <c r="C29" s="5" t="n"/>
+    </row>
+    <row r="30" ht="18" customHeight="1">
+      <c r="B30" s="8" t="inlineStr">
+        <is>
+          <t>Practice</t>
+        </is>
+      </c>
+      <c r="C30" s="7" t="inlineStr">
+        <is>
+          <t>13 practice tasks, each with a Check cell.</t>
+        </is>
+      </c>
     </row>
     <row r="31" ht="18" customHeight="1">
       <c r="B31" s="8" t="inlineStr">
         <is>
-          <t>Practice</t>
+          <t>ED_Hourly</t>
         </is>
       </c>
       <c r="C31" s="7" t="inlineStr">
         <is>
-          <t>13 practice tasks, each with a Check cell.</t>
+          <t>Data: 24 rows, in the Excel Table 'tblEDHourly'</t>
         </is>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
       <c r="B32" s="8" t="inlineStr">
         <is>
-          <t>ED_Hourly</t>
+          <t>ED_Monthly</t>
         </is>
       </c>
       <c r="C32" s="7" t="inlineStr">
         <is>
-          <t>Data: 24 rows, in the Excel Table 'tblEDHourly'</t>
+          <t>Data: 24 rows, in the Excel Table 'tblEDMonthly'</t>
         </is>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
       <c r="B33" s="8" t="inlineStr">
         <is>
-          <t>ED_Monthly</t>
+          <t>Readmits</t>
         </is>
       </c>
       <c r="C33" s="7" t="inlineStr">
         <is>
-          <t>Data: 24 rows, in the Excel Table 'tblEDMonthly'</t>
+          <t>Data: 8 rows, in the Excel Table 'tblReadmits'</t>
         </is>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
       <c r="B34" s="8" t="inlineStr">
         <is>
-          <t>Readmits</t>
+          <t>Makeover</t>
         </is>
       </c>
       <c r="C34" s="7" t="inlineStr">
         <is>
-          <t>Data: 8 rows, in the Excel Table 'tblReadmits'</t>
+          <t>A misleading chart of the 2025 readmission rates. Measure it for Task 4, then fix it in place.</t>
         </is>
       </c>
     </row>
@@ -3778,10 +3778,10 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="49" customHeight="1">
       <c r="A3" s="15" t="inlineStr">
         <is>
-          <t>Type a formula or value in each yellow cell. The Check column turns green when your answer matches. Stuck? Read the hint, then the lesson guide. Answers: right-click a sheet tab → Unhide… → 'Bonus Key'.</t>
+          <t>For B1, fill the yellow LWBSRate column on ED_Monthly, and the gray cell here reads it. For B2–B5, build the charts on ED_Monthly and Denials, then type what they show in the yellow cell. The Check column turns green when your answer matches. Stuck? Read the hint, then the lesson guide. Answers: right-click a sheet tab → Unhide… → 'Bonus Key' (or 'Chart Key' for the reference charts).</t>
         </is>
       </c>
     </row>
@@ -3851,12 +3851,12 @@
       </c>
       <c r="B7" s="19" t="inlineStr">
         <is>
-          <t>Build a combo chart on ED_Monthly with Total as clustered columns and LWBSRate as a line on the secondary axis (select Month, then Ctrl+click or ⌘+click Total and LWBSRate). Which month had the highest LWBS rate? Type the month and year.</t>
+          <t>Build a combo chart on ED_Monthly with Total as clustered columns and LWBSRate as a line on the secondary axis (select Month, then Ctrl + click or ⌘ + click Total and LWBSRate). Which month had the highest LWBS rate? Type the month and year.</t>
         </is>
       </c>
       <c r="C7" s="20" t="inlineStr">
         <is>
-          <t>Select A1:A25, Ctrl+click E1:E25 and G1:G25, then Insert → Insert Combo Chart</t>
+          <t>Select A1:A25, Ctrl + click E1:E25 and G1:G25, then Insert → Insert Combo Chart</t>
         </is>
       </c>
       <c r="D7" s="23" t="n"/>
@@ -3878,7 +3878,7 @@
       </c>
       <c r="C8" s="20" t="inlineStr">
         <is>
-          <t>Select E1:E25, Ctrl+click G1:G25, then Insert → Scatter. RSQ(known_y's, known_x's) confirms it</t>
+          <t>Select E1:E25, Ctrl + click G1:G25, then Insert → Scatter. RSQ(known_y's, known_x's) confirms it</t>
         </is>
       </c>
       <c r="D8" s="45" t="n"/>
@@ -4084,7 +4084,7 @@
       </c>
       <c r="B7" s="19" t="inlineStr">
         <is>
-          <t>On Readmits, sort the table by ReadmitRate from largest to smallest. Then select ServiceLine and ReadmitRate (A1:A9, then Ctrl+click D1:D9, or ⌘+click on a Mac) and insert a clustered bar chart. Before you change anything else, which service line's bar is at the TOP of the chart? (Afterwards, fix the order so the highest rate is on top.)</t>
+          <t>On Readmits, sort the table by ReadmitRate from largest to smallest. Then select ServiceLine and ReadmitRate (A1:A9, then Ctrl + click D1:D9, or ⌘ + click on a Mac) and insert a clustered bar chart. Before you change anything else, which service line's bar is at the TOP of the chart? (Afterwards, fix the order so the highest rate is on top.)</t>
         </is>
       </c>
       <c r="C7" s="49" t="inlineStr">
@@ -4543,7 +4543,7 @@
       </c>
       <c r="B6" s="19" t="inlineStr">
         <is>
-          <t>Build a combo chart on ED_Monthly with Total as clustered columns and LWBSRate as a line on the secondary axis (select Month, then Ctrl+click or ⌘+click Total and LWBSRate). Which month had the highest LWBS rate? Type the month and year.</t>
+          <t>Build a combo chart on ED_Monthly with Total as clustered columns and LWBSRate as a line on the secondary axis (select Month, then Ctrl + click or ⌘ + click Total and LWBSRate). Which month had the highest LWBS rate? Type the month and year.</t>
         </is>
       </c>
       <c r="C6" s="51" t="n">
@@ -4583,7 +4583,7 @@
       </c>
       <c r="D7" s="50" t="inlineStr">
         <is>
-          <t>1. Select E1:E25, then Ctrl+click (Mac: ⌘+click) G1:G25. The left column (Total) becomes X.
+          <t>1. Select E1:E25, then Ctrl + click (Mac: ⌘ + click) G1:G25. The left column (Total) becomes X.
 2. Choose Insert → Insert Scatter (X, Y) or Bubble Chart → Scatter.
 3. Right-click a point → Add Trendline… → Linear, tick Display R-squared value on chart.
 4. Confirm: =RSQ(ED_Monthly!G2:G25,ED_Monthly!E2:E25).</t>
@@ -4617,7 +4617,7 @@
         <is>
           <t>1. Click a DeniedCharges cell → Data → Sort Largest to Smallest.
 2. In D2 type =SUM($C$2:C2)/SUM($C$2:$C$8) and press Enter. The Table fills it down, and the column is already formatted as a percentage.
-3. Select A1:A8, then Ctrl+click (Mac: ⌘+click) C1:D8, and choose Insert → Insert Combo Chart → Clustered Column – Line on Secondary Axis.
+3. Select A1:A8, then Ctrl + click (Mac: ⌘ + click) C1:D8, and choose Insert → Insert Combo Chart → Clustered Column – Line on Secondary Axis.
 4. Double-click the secondary axis and set Minimum 0 and Maximum 1. Optionally set the column Gap Width to about 10%.
 5. Find the first bar where the line reaches 80%.</t>
         </is>
@@ -6109,7 +6109,7 @@
       </c>
       <c r="B8" s="19" t="inlineStr">
         <is>
-          <t>On Readmits, sort the table by ReadmitRate from largest to smallest. Then select ServiceLine and ReadmitRate (A1:A9, then Ctrl+click D1:D9, or ⌘+click on a Mac) and insert a clustered bar chart. Before you change anything else, which service line's bar is at the TOP of the chart? (Afterwards, fix the order so the highest rate is on top.)</t>
+          <t>On Readmits, sort the table by ReadmitRate from largest to smallest. Then select ServiceLine and ReadmitRate (A1:A9, then Ctrl + click D1:D9, or ⌘ + click on a Mac) and insert a clustered bar chart. Before you change anything else, which service line's bar is at the TOP of the chart? (Afterwards, fix the order so the highest rate is on top.)</t>
         </is>
       </c>
       <c r="C8" s="20" t="inlineStr">
@@ -6312,7 +6312,7 @@
       </c>
       <c r="C17" s="20" t="inlineStr">
         <is>
-          <t>Insert → Sparklines → Line. Then the Sparkline tab → Show → First Point, Last Point</t>
+          <t>Insert → Sparklines → Line. Then tick First Point and Last Point on the Sparkline tab</t>
         </is>
       </c>
       <c r="D17" s="21" t="n"/>
